--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="44">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>12.90%</t>
+    <t>19.35%</t>
   </si>
   <si>
     <t xml:space="preserve">Butaca Central B </t>
   </si>
   <si>
-    <t>34.95%</t>
+    <t>35.44%</t>
   </si>
   <si>
     <t>Butaca Lateral A</t>
@@ -100,7 +100,7 @@
     <t>Butaca Lateral C</t>
   </si>
   <si>
-    <t>16.67%</t>
+    <t>16.95%</t>
   </si>
   <si>
     <t>General-Gradas</t>
@@ -142,7 +142,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>42.70%</t>
+    <t>43.05%</t>
   </si>
 </sst>
 </file>
@@ -654,8 +654,8 @@
       <c r="B6" s="6">
         <v>248</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
+      <c r="C6" s="6">
+        <v>16</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -694,10 +694,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="6">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -723,13 +723,13 @@
         <v>22</v>
       </c>
       <c r="G7" s="6">
-        <v>1111</v>
+        <v>1128</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -744,16 +744,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1216</v>
+        <v>1233</v>
       </c>
       <c r="Q7" s="6">
-        <v>2263</v>
+        <v>2246</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -835,7 +835,7 @@
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
@@ -862,10 +862,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q9" s="6">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>

--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="44">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,31 +82,31 @@
     <t>-</t>
   </si>
   <si>
-    <t>19.35%</t>
+    <t>25.81%</t>
   </si>
   <si>
     <t xml:space="preserve">Butaca Central B </t>
   </si>
   <si>
-    <t>35.44%</t>
+    <t>43.17%</t>
   </si>
   <si>
     <t>Butaca Lateral A</t>
   </si>
   <si>
-    <t>19.86%</t>
+    <t>26.27%</t>
   </si>
   <si>
     <t>Butaca Lateral C</t>
   </si>
   <si>
-    <t>16.95%</t>
+    <t>20.36%</t>
   </si>
   <si>
     <t>General-Gradas</t>
   </si>
   <si>
-    <t>56.54%</t>
+    <t>60.78%</t>
   </si>
   <si>
     <t>Palco Nivel 1</t>
@@ -142,7 +142,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>43.05%</t>
+    <t>48.16%</t>
   </si>
 </sst>
 </file>
@@ -690,14 +690,14 @@
       <c r="N6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+      <c r="O6" s="6">
+        <v>16</v>
       </c>
       <c r="P6" s="6">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="Q6" s="6">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -716,8 +716,8 @@
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
+      <c r="E7" s="6">
+        <v>66</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -729,7 +729,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>102</v>
+        <v>271</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -744,16 +744,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1233</v>
+        <v>1502</v>
       </c>
       <c r="Q7" s="6">
-        <v>2246</v>
+        <v>1977</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -772,8 +772,8 @@
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
+      <c r="E8" s="6">
+        <v>114</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -785,7 +785,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -799,17 +799,17 @@
       <c r="M8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="6">
-        <v>142</v>
+      <c r="N8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>285</v>
+        <v>377</v>
       </c>
       <c r="Q8" s="6">
-        <v>1150</v>
+        <v>1058</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -828,8 +828,8 @@
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
+      <c r="E9" s="6">
+        <v>46</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -841,7 +841,7 @@
         <v>22</v>
       </c>
       <c r="I9" s="6">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -855,17 +855,17 @@
       <c r="M9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="6">
-        <v>160</v>
+      <c r="N9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="Q9" s="6">
-        <v>1191</v>
+        <v>1142</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -897,7 +897,7 @@
         <v>22</v>
       </c>
       <c r="I10" s="6">
-        <v>3</v>
+        <v>633</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -912,16 +912,16 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>1530</v>
+        <v>1015</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>1534</v>
+        <v>1649</v>
       </c>
       <c r="Q10" s="6">
-        <v>1179</v>
+        <v>1064</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>

--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="44">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,31 +82,31 @@
     <t>-</t>
   </si>
   <si>
-    <t>25.81%</t>
+    <t>44.76%</t>
   </si>
   <si>
     <t xml:space="preserve">Butaca Central B </t>
   </si>
   <si>
-    <t>43.17%</t>
+    <t>87.27%</t>
   </si>
   <si>
     <t>Butaca Lateral A</t>
   </si>
   <si>
-    <t>26.27%</t>
+    <t>68.29%</t>
   </si>
   <si>
     <t>Butaca Lateral C</t>
   </si>
   <si>
-    <t>20.36%</t>
+    <t>56.35%</t>
   </si>
   <si>
     <t>General-Gradas</t>
   </si>
   <si>
-    <t>60.78%</t>
+    <t>63.44%</t>
   </si>
   <si>
     <t>Palco Nivel 1</t>
@@ -127,7 +127,7 @@
     <t>Palco Presi</t>
   </si>
   <si>
-    <t>0.00%</t>
+    <t>41.30%</t>
   </si>
   <si>
     <t>Suite Cerrada</t>
@@ -142,7 +142,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>48.16%</t>
+    <t>74.53%</t>
   </si>
 </sst>
 </file>
@@ -655,13 +655,13 @@
         <v>248</v>
       </c>
       <c r="C6" s="6">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
+      <c r="E6" s="6">
+        <v>40</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -690,14 +690,14 @@
       <c r="N6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="6">
-        <v>16</v>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="Q6" s="6">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -710,14 +710,14 @@
       <c r="B7" s="6">
         <v>3479</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
+      <c r="C7" s="6">
+        <v>1325</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -744,16 +744,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>37</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+        <v>212</v>
+      </c>
+      <c r="O7" s="6">
+        <v>2</v>
       </c>
       <c r="P7" s="6">
-        <v>1502</v>
+        <v>3036</v>
       </c>
       <c r="Q7" s="6">
-        <v>1977</v>
+        <v>443</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -766,14 +766,14 @@
       <c r="B8" s="6">
         <v>1435</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
+      <c r="C8" s="6">
+        <v>519</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -799,17 +799,17 @@
       <c r="M8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>22</v>
+      <c r="N8" s="6">
+        <v>80</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>377</v>
+        <v>980</v>
       </c>
       <c r="Q8" s="6">
-        <v>1058</v>
+        <v>455</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -822,8 +822,8 @@
       <c r="B9" s="6">
         <v>1434</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
+      <c r="C9" s="6">
+        <v>458</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -855,17 +855,17 @@
       <c r="M9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>22</v>
+      <c r="N9" s="6">
+        <v>58</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>292</v>
+        <v>808</v>
       </c>
       <c r="Q9" s="6">
-        <v>1142</v>
+        <v>626</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -878,8 +878,8 @@
       <c r="B10" s="6">
         <v>2713</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
+      <c r="C10" s="6">
+        <v>48</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -897,7 +897,7 @@
         <v>22</v>
       </c>
       <c r="I10" s="6">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -912,16 +912,16 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>1015</v>
+        <v>1038</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>1649</v>
+        <v>1721</v>
       </c>
       <c r="Q10" s="6">
-        <v>1064</v>
+        <v>992</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -1108,8 +1108,8 @@
       <c r="D14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
+      <c r="E14" s="6">
+        <v>19</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
@@ -1141,11 +1141,11 @@
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P14" s="6" t="s">
-        <v>22</v>
+      <c r="P14" s="6">
+        <v>19</v>
       </c>
       <c r="Q14" s="6">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>38</v>

--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="39">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,48 +82,33 @@
     <t>-</t>
   </si>
   <si>
-    <t>44.76%</t>
+    <t>78.23%</t>
   </si>
   <si>
     <t xml:space="preserve">Butaca Central B </t>
   </si>
   <si>
-    <t>87.27%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Butaca Lateral A</t>
   </si>
   <si>
-    <t>68.29%</t>
-  </si>
-  <si>
     <t>Butaca Lateral C</t>
   </si>
   <si>
-    <t>56.35%</t>
-  </si>
-  <si>
     <t>General-Gradas</t>
   </si>
   <si>
-    <t>63.44%</t>
-  </si>
-  <si>
     <t>Palco Nivel 1</t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
     <t>Palco Nivel 2</t>
   </si>
   <si>
     <t>Palco Nivel 3</t>
   </si>
   <si>
-    <t>98.68%</t>
-  </si>
-  <si>
     <t>Palco Presi</t>
   </si>
   <si>
@@ -142,7 +127,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>74.53%</t>
+    <t>99.14%</t>
   </si>
 </sst>
 </file>
@@ -655,13 +640,13 @@
         <v>248</v>
       </c>
       <c r="C6" s="6">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -687,17 +672,17 @@
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+      <c r="N6" s="6">
+        <v>32</v>
+      </c>
+      <c r="O6" s="6">
+        <v>3</v>
       </c>
       <c r="P6" s="6">
-        <v>111</v>
+        <v>194</v>
       </c>
       <c r="Q6" s="6">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -711,13 +696,13 @@
         <v>3479</v>
       </c>
       <c r="C7" s="6">
-        <v>1325</v>
+        <v>1770</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -729,7 +714,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -744,16 +729,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="O7" s="6">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="P7" s="6">
-        <v>3036</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>443</v>
+        <v>3479</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -767,13 +752,13 @@
         <v>1435</v>
       </c>
       <c r="C8" s="6">
-        <v>519</v>
+        <v>897</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -785,7 +770,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>205</v>
+        <v>251</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -800,36 +785,36 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>80</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
+        <v>84</v>
+      </c>
+      <c r="O8" s="6">
+        <v>15</v>
       </c>
       <c r="P8" s="6">
-        <v>980</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>455</v>
+        <v>1435</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6">
         <v>1434</v>
       </c>
       <c r="C9" s="6">
-        <v>458</v>
+        <v>1015</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -841,7 +826,7 @@
         <v>22</v>
       </c>
       <c r="I9" s="6">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -856,30 +841,30 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>58</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
+        <v>74</v>
+      </c>
+      <c r="O9" s="6">
+        <v>7</v>
       </c>
       <c r="P9" s="6">
-        <v>808</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>626</v>
+        <v>1434</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6">
         <v>2713</v>
       </c>
       <c r="C10" s="6">
-        <v>48</v>
+        <v>998</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -914,22 +899,22 @@
       <c r="N10" s="6">
         <v>1038</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
+      <c r="O10" s="6">
+        <v>42</v>
       </c>
       <c r="P10" s="6">
-        <v>1721</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>992</v>
+        <v>2713</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6">
         <v>177</v>
@@ -980,12 +965,12 @@
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6">
         <v>210</v>
@@ -1036,12 +1021,12 @@
         <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" s="6">
         <v>456</v>
@@ -1059,7 +1044,7 @@
         <v>22</v>
       </c>
       <c r="G13" s="6">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
@@ -1086,18 +1071,18 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>450</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>6</v>
+        <v>456</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B14" s="6">
         <v>46</v>
@@ -1148,12 +1133,12 @@
         <v>27</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6">
         <v>130</v>
@@ -1204,12 +1189,12 @@
         <v>10</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6">
         <v>256</v>
@@ -1260,12 +1245,12 @@
         <v>22</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B17" s="7">
         <f>SUM(B6:B16)</f>
@@ -1316,7 +1301,7 @@
         <f>SUM(Q6:Q16)</f>
       </c>
       <c r="R17" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="39">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -640,7 +640,7 @@
         <v>248</v>
       </c>
       <c r="C6" s="6">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -675,8 +675,8 @@
       <c r="N6" s="6">
         <v>32</v>
       </c>
-      <c r="O6" s="6">
-        <v>3</v>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
         <v>194</v>
@@ -696,7 +696,7 @@
         <v>3479</v>
       </c>
       <c r="C7" s="6">
-        <v>1770</v>
+        <v>1787</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -732,7 +732,7 @@
         <v>187</v>
       </c>
       <c r="O7" s="6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="P7" s="6">
         <v>3479</v>
@@ -752,7 +752,7 @@
         <v>1435</v>
       </c>
       <c r="C8" s="6">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -787,8 +787,8 @@
       <c r="N8" s="6">
         <v>84</v>
       </c>
-      <c r="O8" s="6">
-        <v>15</v>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
         <v>1435</v>
@@ -808,7 +808,7 @@
         <v>1434</v>
       </c>
       <c r="C9" s="6">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -844,7 +844,7 @@
         <v>74</v>
       </c>
       <c r="O9" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P9" s="6">
         <v>1434</v>
@@ -864,7 +864,7 @@
         <v>2713</v>
       </c>
       <c r="C10" s="6">
-        <v>998</v>
+        <v>1040</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -899,8 +899,8 @@
       <c r="N10" s="6">
         <v>1038</v>
       </c>
-      <c r="O10" s="6">
-        <v>42</v>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
         <v>2713</v>

--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -696,7 +696,7 @@
         <v>3479</v>
       </c>
       <c r="C7" s="6">
-        <v>1787</v>
+        <v>1810</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -729,7 +729,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="O7" s="6">
         <v>2</v>
@@ -752,7 +752,7 @@
         <v>1435</v>
       </c>
       <c r="C8" s="6">
-        <v>912</v>
+        <v>936</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -785,7 +785,7 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
@@ -808,7 +808,7 @@
         <v>1434</v>
       </c>
       <c r="C9" s="6">
-        <v>1021</v>
+        <v>1060</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -841,7 +841,7 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="O9" s="6">
         <v>1</v>
@@ -864,7 +864,7 @@
         <v>2713</v>
       </c>
       <c r="C10" s="6">
-        <v>1040</v>
+        <v>1058</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -897,7 +897,7 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>

--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="37">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,15 +82,12 @@
     <t>-</t>
   </si>
   <si>
-    <t>78.23%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t xml:space="preserve">Butaca Central B </t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
     <t>Butaca Lateral A</t>
   </si>
   <si>
@@ -112,9 +109,6 @@
     <t>Palco Presi</t>
   </si>
   <si>
-    <t>41.30%</t>
-  </si>
-  <si>
     <t>Suite Cerrada</t>
   </si>
   <si>
@@ -127,7 +121,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>99.14%</t>
+    <t>99.91%</t>
   </si>
 </sst>
 </file>
@@ -646,7 +640,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -679,10 +673,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>194</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>54</v>
+        <v>248</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -696,19 +690,19 @@
         <v>3479</v>
       </c>
       <c r="C7" s="6">
-        <v>1810</v>
+        <v>1940</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="6">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>22</v>
@@ -728,11 +722,11 @@
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="6">
-        <v>164</v>
-      </c>
-      <c r="O7" s="6">
-        <v>2</v>
+      <c r="N7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
         <v>3479</v>
@@ -741,24 +735,24 @@
         <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6">
         <v>1435</v>
       </c>
       <c r="C8" s="6">
-        <v>936</v>
+        <v>958</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -784,8 +778,8 @@
       <c r="M8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="6">
-        <v>60</v>
+      <c r="N8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
@@ -797,24 +791,24 @@
         <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="6">
         <v>1434</v>
       </c>
       <c r="C9" s="6">
-        <v>1060</v>
+        <v>1081</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -840,11 +834,11 @@
       <c r="M9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="6">
-        <v>35</v>
-      </c>
-      <c r="O9" s="6">
-        <v>1</v>
+      <c r="N9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P9" s="6">
         <v>1434</v>
@@ -853,12 +847,12 @@
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="6">
         <v>2713</v>
@@ -909,12 +903,12 @@
         <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6">
         <v>177</v>
@@ -965,12 +959,12 @@
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6">
         <v>210</v>
@@ -1021,12 +1015,12 @@
         <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="6">
         <v>456</v>
@@ -1077,12 +1071,12 @@
         <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="6">
         <v>46</v>
@@ -1094,7 +1088,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="6">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
@@ -1127,18 +1121,18 @@
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>27</v>
+        <v>46</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15" s="6">
         <v>130</v>
@@ -1189,12 +1183,12 @@
         <v>10</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6">
         <v>256</v>
@@ -1245,12 +1239,12 @@
         <v>22</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" s="7">
         <f>SUM(B6:B16)</f>
@@ -1301,7 +1295,7 @@
         <f>SUM(Q6:Q16)</f>
       </c>
       <c r="R17" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="35">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -112,16 +112,10 @@
     <t>Suite Cerrada</t>
   </si>
   <si>
-    <t>92.31%</t>
-  </si>
-  <si>
     <t>Suite Terraza</t>
   </si>
   <si>
     <t>TOTALES</t>
-  </si>
-  <si>
-    <t>99.91%</t>
   </si>
 </sst>
 </file>
@@ -646,7 +640,7 @@
         <v>22</v>
       </c>
       <c r="G6" s="6">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>22</v>
@@ -666,8 +660,8 @@
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6">
-        <v>32</v>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
@@ -1143,8 +1137,8 @@
       <c r="D15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>22</v>
+      <c r="E15" s="6">
+        <v>10</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>22</v>
@@ -1177,18 +1171,18 @@
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>120</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>10</v>
+        <v>130</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="6">
         <v>256</v>
@@ -1244,7 +1238,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="7">
         <f>SUM(B6:B16)</f>
@@ -1295,7 +1289,7 @@
         <f>SUM(Q6:Q16)</f>
       </c>
       <c r="R17" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Saraperos 2026.xlsx
+++ b/data/asistencia/Saraperos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="37">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -97,6 +97,9 @@
     <t>General-Gradas</t>
   </si>
   <si>
+    <t>99.82%</t>
+  </si>
+  <si>
     <t>Palco Nivel 1</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
   </si>
   <si>
     <t>TOTALES</t>
+  </si>
+  <si>
+    <t>99.95%</t>
   </si>
 </sst>
 </file>
@@ -885,24 +891,24 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>2713</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>22</v>
+        <v>2708</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>5</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6">
         <v>177</v>
@@ -958,7 +964,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6">
         <v>210</v>
@@ -1014,7 +1020,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="6">
         <v>456</v>
@@ -1070,7 +1076,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="6">
         <v>46</v>
@@ -1126,7 +1132,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6">
         <v>130</v>
@@ -1182,7 +1188,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6">
         <v>256</v>
@@ -1238,7 +1244,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="7">
         <f>SUM(B6:B16)</f>
@@ -1289,7 +1295,7 @@
         <f>SUM(Q6:Q16)</f>
       </c>
       <c r="R17" s="7" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
